--- a/tiflow/move-configuration-requirements/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/move-configuration-requirements/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:17:40+00:00</t>
+    <t>2026-06-25T08:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/move-configuration-requirements/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/move-configuration-requirements/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:46:54+00:00</t>
+    <t>2026-06-25T09:58:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
